--- a/devComs/oli-obk_commits.xlsx
+++ b/devComs/oli-obk_commits.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C126"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-02T14:57:49+00:00</t>
+          <t>2026-04-21T21:01:21+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Track import map per-owner</t>
+          <t>Use shorter borrows for `FnKind`</t>
         </is>
       </c>
     </row>
@@ -458,12 +458,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-02T15:20:22+00:00</t>
+          <t>2026-05-13T14:33:17+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rename and document a relaxed bound reason</t>
+          <t>simplify ast validation struct visiting</t>
         </is>
       </c>
     </row>
@@ -475,12 +475,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-02T11:59:11+00:00</t>
+          <t>2026-05-12T14:12:53+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eagerly decide whether relaxed bounds are allowed or not</t>
+          <t>Infer all anonymous lifetimes in (assoc) consts as `'static`  Hard error on hidden elided lifetimes (`S` instead of `S&lt;'_&gt;`) in assoc consts</t>
         </is>
       </c>
     </row>
@@ -492,12 +492,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-02T11:59:11+00:00</t>
+          <t>2026-07-09T10:27:19+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Track trait map per-owner</t>
+          <t>Use `as_lang_item` instead of repeatedly matching</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-28T08:34:07+00:00</t>
+          <t>2026-07-09T10:02:23+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Track `lifetimes_res_map` per owner</t>
+          <t>Eagerly collect missing weak lang items and trim that small list instead of revisiting the entire ast</t>
         </is>
       </c>
     </row>
@@ -526,12 +526,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-28T08:23:14+00:00</t>
+          <t>2026-07-09T09:13:13+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Track `label_res_map` per-owner</t>
+          <t>Special case the two weak lang item oddities we have</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-27T11:22:12+00:00</t>
+          <t>2026-07-09T09:05:18+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Track `lifetime_elision_allowed` per owner, and discard fn ptr and `Fn()` syntax registrations of it, they are never used</t>
+          <t>Documentation fix</t>
         </is>
       </c>
     </row>
@@ -560,12 +560,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-29T08:24:51+00:00</t>
+          <t>2026-07-09T09:41:29+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Use default field values to avoid some churn</t>
+          <t>Enforce using the correct target for lang attr on foreign items</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-28T10:25:53+00:00</t>
+          <t>2026-07-09T08:56:54+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eagerly resolve delegations in late resolution</t>
+          <t>Reuse existing methods or create corresponding ones where other nodes already have them</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-12T13:39:25+00:00</t>
+          <t>2026-07-09T08:48:11+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>extra_lifetime_params_map can only ever contain `LifetimeRes::Fresh`, so just encode the fields we need</t>
+          <t>Use the already existing source span, which is good enough for lang item diagnostics</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-12T13:37:28+00:00</t>
+          <t>2026-07-09T08:31:41+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remove an unused field</t>
+          <t>Use the AssocCtxt instead of looking at the parent</t>
         </is>
       </c>
     </row>
@@ -628,12 +628,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-12T13:19:31+00:00</t>
+          <t>2026-07-09T08:22:09+00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remove some dead code</t>
+          <t>Adjust query description</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-12T10:38:57+00:00</t>
+          <t>2026-07-09T08:19:44+00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Drop an unused distinction (in diagnostics code) between anonymous and named lifetimes</t>
+          <t>Remove some query ensure_dones that are also performed by index_ast</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-26T11:14:02+00:00</t>
+          <t>2026-06-24T14:37:31+00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rename and document some methods</t>
+          <t>Add a convenience helper for doing type ops</t>
         </is>
       </c>
     </row>
@@ -679,12 +679,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-12T10:31:24+00:00</t>
+          <t>2026-06-24T10:38:01+00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Add a dedicated method for error lifetime recording</t>
+          <t>Don't compute opaque types for typeck children. They are always the same as their parent</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-05-11T07:39:54+00:00</t>
+          <t>2026-06-24T10:17:24+00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remove an unnecessary generic</t>
+          <t>Typeck children always have the same param env as their parent</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-05-11T06:53:22+00:00</t>
+          <t>2026-06-24T07:10:13+00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Merge two functions always called after each other</t>
+          <t>Remove some unnecessary mutabilities</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-07T13:31:23+00:00</t>
+          <t>2026-06-24T07:10:13+00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stop putting owner's `DefId` into their own `node_id_to_def_id` map  Now they unfortunately land in their parent, which is not necessary</t>
+          <t>Consistently taint root cx  Instead of having to taint both infcx and root_cx, we always just taint infcx (which usually gets automatically tainted from emitting diagnostics), and at the end (before dropping the infcx) we move the taint over to the root_cx</t>
         </is>
       </c>
     </row>
@@ -747,12 +747,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-02-17T11:57:28+00:00</t>
+          <t>2026-06-23T14:37:49+00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Split the resolver tables into per-owner tables, starting with `node_id_to_def_id`</t>
+          <t>Move some methods that only need the region context onto that</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-04T15:56:47+00:00</t>
+          <t>2026-06-22T15:49:19+00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Make `UnordItems::flat_map` take `UnordItems` as args, too</t>
+          <t>Only load the feature list once in the entire resolver</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-04T15:56:47+00:00</t>
+          <t>2026-06-02T08:16:10+00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Make `UnordItems::flat_map` take `UnordItems` as args, too</t>
+          <t>Use an unexpanded span for actually written down opt out params</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-05T05:23:24+00:00</t>
+          <t>2026-06-18T09:57:14+00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Follow-up cleanups reusing the now-available `LocalDefId`s</t>
+          <t>Point to the unstable segment of an import path instead of to the whole path</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-05T04:15:58+00:00</t>
+          <t>2026-06-17T07:16:43+00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avoid hitting the global node_id_to_def_id table for unused macros</t>
+          <t>Reject `impl const Trait` since the right syntax is `const impl Trait` now</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-05T04:36:36+00:00</t>
+          <t>2026-06-16T16:03:46+00:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avoid using `id` followed by `local_def_id` if we can just call `def_id` instead</t>
+          <t>Avoid loading HIR from a table when it's already available</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-05T04:31:19+00:00</t>
+          <t>2026-06-16T15:49:06+00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avoid some global `node_id_to_def_id` lookups in import resolution</t>
+          <t>Share some more logic between hir expr/pat/ty paths</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-04T14:28:16+00:00</t>
+          <t>2026-06-02T10:50:22+00:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Use `all_impls` instead of handrolling it</t>
+          <t>Add expansion info to assoc type default bounds</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-04-28T08:14:24+00:00</t>
+          <t>2026-06-02T08:16:10+00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Revert const hack and use const closure</t>
+          <t>Add expansion info to default bounds</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-04-27T07:19:56+00:00</t>
+          <t>2026-06-02T08:28:51+00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remove const closure hacks in libstd</t>
+          <t>Exhaustively match on `DesugaringKind`</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-04T08:37:46+00:00</t>
+          <t>2026-06-02T11:03:09+00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remove most uses of `def_id_to_node_id`  Especially those happening during normal resolving, where we are actually looking at current parent scopes</t>
+          <t>Generalize where bound handling</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-04T08:30:16+00:00</t>
+          <t>2026-06-10T10:06:08+00:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Add NodeId to ModuleKind</t>
+          <t>Remove an unnecessary cloning</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-02-13T11:25:14+00:00</t>
+          <t>2026-06-08T15:21:09+00:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rip out rustc_layout_scalar_valid_range_* attribute support</t>
+          <t>Mark more reflection things as comptime</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-02-13T11:25:14+00:00</t>
+          <t>2026-06-08T10:21:58+00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rip out rustc_layout_scalar_valid_range_* attribute support</t>
+          <t>Mark `trait_info_of` as comptime and adjust the compiler to handle it</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-17T11:29:17+00:00</t>
+          <t>2026-06-08T14:59:40+00:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remove rustc_layout_scalar_valid_range attr from debuginfo</t>
+          <t>Add a regression test</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-16T11:09:51+00:00</t>
+          <t>2026-06-02T11:19:52+00:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remove mir-opt mention of rustc_scalar_layout attr</t>
+          <t>Report duplicate relaxed bounds during ast lowering</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-16T11:07:33+00:00</t>
+          <t>2026-06-02T11:42:14+00:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Stop using `rustc_scalar_layout` in enum test</t>
+          <t>Add more tests</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-16T11:02:35+00:00</t>
+          <t>2026-06-05T13:55:17+00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stop using `rustc_scalar_layout` attr in jump threading test</t>
+          <t>Avoid passing the parent (== owner) node id to `lower_generics` and load it from the per-owner info instead</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-16T10:46:41+00:00</t>
+          <t>2026-05-03T09:52:43+00:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stop using `rustc_scalar_layout` attr in gvn test</t>
+          <t>Remove possibly footgunny `is_const` method</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-27T05:47:56+00:00</t>
+          <t>2026-05-03T09:52:43+00:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Suggest various missing trait bounds on `HostEffect` clauses not being satisfied</t>
+          <t>Remove possibly footgunny `is_const` method</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-25T19:00:51+00:00</t>
+          <t>2025-11-11T12:30:42+00:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Suggest const destruct bounds on `Drop` impls when they are missing</t>
+          <t>Make the `inline` field on the `Const` `ConstContext` more clearly targetted at what it does</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-28T08:31:16+00:00</t>
+          <t>2025-11-11T12:30:42+00:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Handle hkl const closures</t>
+          <t>Make the `inline` field on the `Const` `ConstContext` more clearly targetted at what it does</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-28T08:24:58+00:00</t>
+          <t>2025-11-11T12:13:50+00:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Add regression test for hkl const closures</t>
+          <t>Demonstrate that `const Trait` bounds allow trait methods to be called in comptime fn</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-27T08:25:20+00:00</t>
+          <t>2025-11-05T16:55:03+00:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Render `ConstContext` for diagnostics once  instead of duplicating in every diagnostic</t>
+          <t>Allow comptime fns to call other comptime fns</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-25T10:52:15+00:00</t>
+          <t>2025-11-05T16:32:38+00:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Check closure's constness validity in the `constness` query  instead of during ast lowering, where it's not easily possible to obtain all the right information in time</t>
+          <t>Prevent comptime fns from being called at runtime</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-25T07:47:07+00:00</t>
+          <t>2026-06-02T14:57:49+00:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Add regression test</t>
+          <t>Track import map per-owner</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-22T15:09:33+00:00</t>
+          <t>2026-06-02T15:20:22+00:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Reject implementing `const Drop` for types that are not const `Destruct` already</t>
+          <t>Rename and document a relaxed bound reason</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-22T14:59:44+00:00</t>
+          <t>2026-06-02T11:59:11+00:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Add regression test</t>
+          <t>Eagerly decide whether relaxed bounds are allowed or not</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-24T10:50:21+00:00</t>
+          <t>2026-06-02T11:59:11+00:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>All generated associated types for opaque types in traits/impls have the same parent</t>
+          <t>Track trait map per-owner</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-21T10:44:13+00:00</t>
+          <t>2026-05-28T08:34:07+00:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>All nested statics in a single interning run have the same parent  So we do not need to disambiguate considering parents</t>
+          <t>Track `lifetimes_res_map` per owner</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-22T10:27:12+00:00</t>
+          <t>2026-05-28T08:23:14+00:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Update a very outdated comment</t>
+          <t>Track `label_res_map` per-owner</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-22T10:08:58+00:00</t>
+          <t>2026-05-27T11:22:12+00:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BinOpAssign always returns unit</t>
+          <t>Track `lifetime_elision_allowed` per owner, and discard fn ptr and `Fn()` syntax registrations of it, they are never used</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-04-21T21:18:10+00:00</t>
+          <t>2026-05-29T08:24:51+00:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remove a bunch of unnecessary explicit lifetimes from the ast validator</t>
+          <t>Use default field values to avoid some churn</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-04-20T12:06:31+00:00</t>
+          <t>2026-05-28T10:25:53+00:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Immediately feed visibility on DefId creation</t>
+          <t>Eagerly resolve delegations in late resolution</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-04-20T13:20:16+00:00</t>
+          <t>2026-05-12T13:39:25+00:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Handle MacCall items directly in the def collector  instead of entangling it with the brg logic</t>
+          <t>extra_lifetime_params_map can only ever contain `LifetimeRes::Fresh`, so just encode the fields we need</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-04-20T13:16:37+00:00</t>
+          <t>2026-05-12T13:37:28+00:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>delegation macros are never handled in the def collector</t>
+          <t>Remove an unused field</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-04-20T12:45:04+00:00</t>
+          <t>2026-05-12T13:19:31+00:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Move variant ctor creation into the brg</t>
+          <t>Remove some dead code</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-04-20T12:27:50+00:00</t>
+          <t>2026-05-12T10:38:57+00:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Stop creating ctor def ids for unions and move the ctor def id creation into the brg</t>
+          <t>Drop an unused distinction (in diagnostics code) between anonymous and named lifetimes</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-04-20T17:44:10+00:00</t>
+          <t>2026-05-26T11:14:02+00:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ensure we don't feed owners from ast lowering if we ever make that query tracked</t>
+          <t>Rename and document some methods</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-04-08T11:14:28+00:00</t>
+          <t>2026-05-12T10:31:24+00:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Handle attributes entirely in the def collector</t>
+          <t>Add a dedicated method for error lifetime recording</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-04-07T10:54:49+00:00</t>
+          <t>2026-05-11T07:39:54+00:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avoid matching on the assoc item kind twice</t>
+          <t>Remove an unnecessary generic</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-04-07T10:51:16+00:00</t>
+          <t>2026-05-11T06:53:22+00:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inline macro calls in assoc item position logic</t>
+          <t>Merge two functions always called after each other</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-04-07T09:51:31+00:00</t>
+          <t>2026-05-07T13:31:23+00:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Deduplicate the `expansion` field between def collection and brg</t>
+          <t>Stop putting owner's `DefId` into their own `node_id_to_def_id` map  Now they unfortunately land in their parent, which is not necessary</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-04-07T09:42:07+00:00</t>
+          <t>2026-02-17T11:57:28+00:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inline the now-trivial build_reduced_graph into its sole caller</t>
+          <t>Split the resolver tables into per-owner tables, starting with `node_id_to_def_id`</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-03-10T14:58:59+00:00</t>
+          <t>2026-05-04T15:56:47+00:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fix use trees</t>
+          <t>Make `UnordItems::flat_map` take `UnordItems` as args, too</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-03-10T14:35:51+00:00</t>
+          <t>2026-05-04T15:56:47+00:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Merge visit_attribute</t>
+          <t>Make `UnordItems::flat_map` take `UnordItems` as args, too</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-03-10T14:27:34+00:00</t>
+          <t>2026-05-05T05:23:24+00:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Merge visit_expr, visit_pat and visit_ty</t>
+          <t>Follow-up cleanups reusing the now-available `LocalDefId`s</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-10T14:26:35+00:00</t>
+          <t>2026-05-05T04:15:58+00:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Merge visit_field_def</t>
+          <t>Avoid hitting the global node_id_to_def_id table for unused macros</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-03-10T14:09:42+00:00</t>
+          <t>2026-05-05T04:36:36+00:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Merge visit_variant</t>
+          <t>Avoid using `id` followed by `local_def_id` if we can just call `def_id` instead</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-03-10T14:07:17+00:00</t>
+          <t>2026-05-05T04:31:19+00:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Merge visit_crate</t>
+          <t>Avoid some global `node_id_to_def_id` lookups in import resolution</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-03-10T14:06:28+00:00</t>
+          <t>2026-05-04T14:28:16+00:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Merge visit_where_predicate</t>
+          <t>Use `all_impls` instead of handrolling it</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-03-10T14:05:50+00:00</t>
+          <t>2026-04-28T08:14:24+00:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Merge visit_generic_param</t>
+          <t>Revert const hack and use const closure</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-03-10T14:02:40+00:00</t>
+          <t>2026-04-27T07:19:56+00:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Merge some simple visitor functions</t>
+          <t>Remove const closure hacks in libstd</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-03-10T14:01:02+00:00</t>
+          <t>2026-05-04T08:37:46+00:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Merge visit_assoc_item</t>
+          <t>Remove most uses of `def_id_to_node_id`  Especially those happening during normal resolving, where we are actually looking at current parent scopes</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-03-10T12:36:44+00:00</t>
+          <t>2026-05-04T08:30:16+00:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Merge visit_block</t>
+          <t>Add NodeId to ModuleKind</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-03-10T12:33:56+00:00</t>
+          <t>2026-02-13T11:25:14+00:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Merge visit_stmt</t>
+          <t>Rip out rustc_layout_scalar_valid_range_* attribute support</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-03-10T12:03:38+00:00</t>
+          <t>2026-02-13T11:25:14+00:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Merge visit_foreign_item</t>
+          <t>Rip out rustc_layout_scalar_valid_range_* attribute support</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-03-10T12:32:07+00:00</t>
+          <t>2026-04-17T11:29:17+00:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Merge visit_item</t>
+          <t>Remove rustc_layout_scalar_valid_range attr from debuginfo</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-02-21T20:05:23+00:00</t>
+          <t>2026-04-16T11:09:51+00:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Merge BuildReducedGraphVisitor initialization into DefPathVisitor</t>
+          <t>Remove mir-opt mention of rustc_scalar_layout attr</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-02-21T19:59:28+00:00</t>
+          <t>2026-04-16T11:07:33+00:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rename DefCollector::resolver to `r` to match `BuildReducedGraphVisitor::r`</t>
+          <t>Stop using `rustc_scalar_layout` in enum test</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-04-15T12:26:06+00:00</t>
+          <t>2026-04-16T11:02:35+00:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Handle non-null pattern types in size skeleton</t>
+          <t>Stop using `rustc_scalar_layout` attr in jump threading test</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-04-15T12:16:18+00:00</t>
+          <t>2026-04-16T10:46:41+00:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Add regression test</t>
+          <t>Stop using `rustc_scalar_layout` attr in gvn test</t>
         </is>
       </c>
     </row>
@@ -1801,12 +1801,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-04-07T07:29:27+00:00</t>
+          <t>2026-04-27T05:47:56+00:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Revert performing basic const checks in typeck on stable</t>
+          <t>Suggest various missing trait bounds on `HostEffect` clauses not being satisfied</t>
         </is>
       </c>
     </row>
@@ -1818,12 +1818,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-03-13T20:58:44+00:00</t>
+          <t>2026-04-25T19:00:51+00:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Use the item span for DefKind::Use, it is never used anyway</t>
+          <t>Suggest const destruct bounds on `Drop` impls when they are missing</t>
         </is>
       </c>
     </row>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-02-21T20:35:15+00:00</t>
+          <t>2026-04-28T08:31:16+00:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Use fine grained component-wise span tracking in use trees</t>
+          <t>Handle hkl const closures</t>
         </is>
       </c>
     </row>
@@ -1852,12 +1852,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-02-21T20:35:15+00:00</t>
+          <t>2026-04-28T08:24:58+00:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Use fine grained component-wise span tracking in use trees</t>
+          <t>Add regression test for hkl const closures</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-13T11:01:54+00:00</t>
+          <t>2026-04-27T08:25:20+00:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Some test cleanups</t>
+          <t>Render `ConstContext` for diagnostics once  instead of duplicating in every diagnostic</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-13T10:23:50+00:00</t>
+          <t>2026-04-25T10:52:15+00:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remove the incomplete marker from const closures</t>
+          <t>Check closure's constness validity in the `constness` query  instead of during ast lowering, where it's not easily possible to obtain all the right information in time</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-13T07:47:24+00:00</t>
+          <t>2026-04-25T07:47:07+00:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Allow calling const closures on the old solver</t>
+          <t>Add regression test</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-13T07:37:12+00:00</t>
+          <t>2026-04-22T15:09:33+00:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Enable the const_closures feature gate to silence an unrelated error</t>
+          <t>Reject implementing `const Drop` for types that are not const `Destruct` already</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-11T07:37:29+00:00</t>
+          <t>2026-04-22T14:59:44+00:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Allow calling const closures in const items</t>
+          <t>Add regression test</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-12T08:38:41+00:00</t>
+          <t>2026-04-24T10:50:21+00:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Const closure's const context is the same as their parent</t>
+          <t>All generated associated types for opaque types in traits/impls have the same parent</t>
         </is>
       </c>
     </row>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-12T08:44:28+00:00</t>
+          <t>2026-04-21T10:44:13+00:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Reject const closures outside const contexts</t>
+          <t>All nested statics in a single interning run have the same parent  So we do not need to disambiguate considering parents</t>
         </is>
       </c>
     </row>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-03-11T07:22:26+00:00</t>
+          <t>2026-04-22T10:27:12+00:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Unconditionally error when trying to create a const coroutine</t>
+          <t>Update a very outdated comment</t>
         </is>
       </c>
     </row>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-03-10T13:51:41+00:00</t>
+          <t>2026-04-22T10:08:58+00:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mark an unreachable match arm as such  Synchronize which elements have code paths and which are unreachable betwen def collector and build reduced graph</t>
+          <t>BinOpAssign always returns unit</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-02-13T10:28:54+00:00</t>
+          <t>2026-04-21T21:18:10+00:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Stop using rustc_layout_scalar_valid_range_* in rustc</t>
+          <t>Remove a bunch of unnecessary explicit lifetimes from the ast validator</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-02-10T09:37:30+00:00</t>
+          <t>2026-04-20T12:06:31+00:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Prevent const stability attrs from being applied to macros via the normal attribute logic instead of special cased checks</t>
+          <t>Immediately feed visibility on DefId creation</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2025-12-04T08:55:33+00:00</t>
+          <t>2026-04-20T13:20:16+00:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Restrict the set of things that const stability can be applied</t>
+          <t>Handle MacCall items directly in the def collector  instead of entangling it with the brg logic</t>
         </is>
       </c>
     </row>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2025-12-04T11:49:56+00:00</t>
+          <t>2026-04-20T13:16:37+00:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remove accidental const stability marker on a struct</t>
+          <t>delegation macros are never handled in the def collector</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-02-07T19:24:59+00:00</t>
+          <t>2026-04-20T12:45:04+00:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Do not require `'static` for obtaining reflection information.</t>
+          <t>Move variant ctor creation into the brg</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2025-11-27T07:51:17+00:00</t>
+          <t>2026-04-20T12:27:50+00:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Perform many const checks in typeck</t>
+          <t>Stop creating ctor def ids for unions and move the ctor def id creation into the brg</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2025-12-03T12:21:03+00:00</t>
+          <t>2026-04-20T17:44:10+00:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>`is_const_default_method` is completely handled by the `constness` query</t>
+          <t>Ensure we don't feed owners from ast lowering if we ever make that query tracked</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2025-11-06T09:00:38+00:00</t>
+          <t>2026-04-08T11:14:28+00:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Add a diagnostic attribute for special casing const bound errors for non-const impls</t>
+          <t>Handle attributes entirely in the def collector</t>
         </is>
       </c>
     </row>
@@ -2158,12 +2158,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2025-11-19T16:02:12+00:00</t>
+          <t>2026-04-07T10:54:49+00:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Add a macro for defaulted enum encoding, use it for hir::Defaultness and deduplicate the logic for other similar enums</t>
+          <t>Avoid matching on the assoc item kind twice</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2025-11-06T12:05:48+00:00</t>
+          <t>2026-04-07T10:51:16+00:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Resolve to a concrete impl instead of using fuzzy search</t>
+          <t>Inline macro calls in assoc item position logic</t>
         </is>
       </c>
     </row>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2025-11-19T16:01:09+00:00</t>
+          <t>2026-04-07T09:51:31+00:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Not encoding the default is already handled by `set`</t>
+          <t>Deduplicate the `expansion` field between def collection and brg</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2025-11-19T15:31:45+00:00</t>
+          <t>2026-04-07T09:42:07+00:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Only encode `hir::Safety::Safe` in metadata.  While `Unsafe` is much less common, a failure to encode it would make downstream crates default to `Safe` and think a thing marked as unsafe is actually safe</t>
+          <t>Inline the now-trivial build_reduced_graph into its sole caller</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2025-11-19T15:28:19+00:00</t>
+          <t>2026-03-10T14:58:59+00:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remove some now-unnecessary impls</t>
+          <t>Fix use trees</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2025-11-18T09:27:51+00:00</t>
+          <t>2026-03-10T14:35:51+00:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avoid encoding non-constness or non-asyncness in metadata</t>
+          <t>Merge visit_attribute</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2260,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2025-10-31T10:50:52+00:00</t>
+          <t>2026-03-10T14:27:34+00:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Give all impls a constness</t>
+          <t>Merge visit_expr, visit_pat and visit_ty</t>
         </is>
       </c>
     </row>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2025-10-31T10:50:52+00:00</t>
+          <t>2026-03-10T14:26:35+00:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Give all impls a constness</t>
+          <t>Merge visit_field_def</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2025-10-31T10:50:52+00:00</t>
+          <t>2026-03-10T14:09:42+00:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Give all impls a constness</t>
+          <t>Merge visit_variant</t>
         </is>
       </c>
     </row>
@@ -2311,12 +2311,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2025-10-30T09:51:50+00:00</t>
+          <t>2026-03-10T14:07:17+00:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fix deferred cast checks using the wrong body for determining constness</t>
+          <t>Merge visit_crate</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2025-10-30T09:33:53+00:00</t>
+          <t>2026-03-10T14:06:28+00:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Show that a test still fails with the feature gate enabled</t>
+          <t>Merge visit_where_predicate</t>
         </is>
       </c>
     </row>
@@ -2345,12 +2345,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2025-10-21T10:17:38+00:00</t>
+          <t>2026-03-10T14:05:50+00:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pattern types have their base type as a field</t>
+          <t>Merge visit_generic_param</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-10-07T12:50:46+00:00</t>
+          <t>2026-03-10T14:02:40+00:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bump ui_test</t>
+          <t>Merge some simple visitor functions</t>
         </is>
       </c>
     </row>
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-10-01T13:50:51+00:00</t>
+          <t>2026-03-10T14:01:02+00:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avoid a bool and use an Option of ZST instead</t>
+          <t>Merge visit_assoc_item</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-10-14T14:29:49+00:00</t>
+          <t>2026-03-10T12:36:44+00:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avoid some needless monomorphizations</t>
+          <t>Merge visit_block</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-10-04T18:11:26+00:00</t>
+          <t>2026-03-10T12:33:56+00:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Prefer refutable slice patterns over len check + index op</t>
+          <t>Merge visit_stmt</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-09-16T21:07:18+00:00</t>
+          <t>2026-03-10T12:03:38+00:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Automatically add/remove labesl when github review (requests) are used</t>
+          <t>Merge visit_foreign_item</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09-16T08:26:42+00:00</t>
+          <t>2026-03-10T12:32:07+00:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Fix run --dep</t>
+          <t>Merge visit_item</t>
         </is>
       </c>
     </row>
@@ -2464,12 +2464,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-09-16T19:10:32+00:00</t>
+          <t>2026-02-21T20:05:23+00:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Refator DependencyBuilder construction</t>
+          <t>Merge BuildReducedGraphVisitor initialization into DefPathVisitor</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-09-07T14:40:08+00:00</t>
+          <t>2026-02-21T19:59:28+00:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bump ui test</t>
+          <t>Rename DefCollector::resolver to `r` to match `BuildReducedGraphVisitor::r`</t>
         </is>
       </c>
     </row>
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-09-08T12:43:12+00:00</t>
+          <t>2026-04-15T12:26:06+00:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remove an unused piece of logic</t>
+          <t>Handle non-null pattern types in size skeleton</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2515,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-08-17T19:38:10+00:00</t>
+          <t>2026-04-15T12:16:18+00:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bump ui_test</t>
+          <t>Add regression test</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-05-02T10:44:40+00:00</t>
+          <t>2026-04-07T07:29:27+00:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bump ui_test to 0.23</t>
+          <t>Revert performing basic const checks in typeck on stable</t>
         </is>
       </c>
     </row>
@@ -2549,10 +2549,741 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
+          <t>2026-03-13T20:58:44+00:00</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Use the item span for DefKind::Use, it is never used anyway</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-02-21T20:35:15+00:00</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Use fine grained component-wise span tracking in use trees</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-02-21T20:35:15+00:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Use fine grained component-wise span tracking in use trees</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-03-13T11:01:54+00:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Some test cleanups</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-03-13T10:23:50+00:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Remove the incomplete marker from const closures</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-03-13T07:47:24+00:00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Allow calling const closures on the old solver</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-03-13T07:37:12+00:00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Enable the const_closures feature gate to silence an unrelated error</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-03-11T07:37:29+00:00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Allow calling const closures in const items</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-03-12T08:38:41+00:00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Const closure's const context is the same as their parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-03-12T08:44:28+00:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Reject const closures outside const contexts</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-03-11T07:22:26+00:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Unconditionally error when trying to create a const coroutine</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-03-10T13:51:41+00:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Mark an unreachable match arm as such  Synchronize which elements have code paths and which are unreachable betwen def collector and build reduced graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-02-13T10:28:54+00:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Stop using rustc_layout_scalar_valid_range_* in rustc</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-02-10T09:37:30+00:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Prevent const stability attrs from being applied to macros via the normal attribute logic instead of special cased checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2025-12-04T08:55:33+00:00</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Restrict the set of things that const stability can be applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2025-12-04T11:49:56+00:00</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Remove accidental const stability marker on a struct</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-02-07T19:24:59+00:00</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Do not require `'static` for obtaining reflection information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2025-11-27T07:51:17+00:00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Perform many const checks in typeck</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2025-12-03T12:21:03+00:00</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>`is_const_default_method` is completely handled by the `constness` query</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2025-11-06T09:00:38+00:00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Add a diagnostic attribute for special casing const bound errors for non-const impls</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2025-11-19T16:02:12+00:00</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Add a macro for defaulted enum encoding, use it for hir::Defaultness and deduplicate the logic for other similar enums</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2025-11-06T12:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Resolve to a concrete impl instead of using fuzzy search</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2025-11-19T16:01:09+00:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Not encoding the default is already handled by `set`</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2025-11-19T15:31:45+00:00</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Only encode `hir::Safety::Safe` in metadata.  While `Unsafe` is much less common, a failure to encode it would make downstream crates default to `Safe` and think a thing marked as unsafe is actually safe</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2025-11-19T15:28:19+00:00</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Remove some now-unnecessary impls</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2025-11-18T09:27:51+00:00</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Avoid encoding non-constness or non-asyncness in metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2025-10-31T10:50:52+00:00</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Give all impls a constness</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2025-10-31T10:50:52+00:00</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Give all impls a constness</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2025-10-31T10:50:52+00:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Give all impls a constness</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2025-10-30T09:51:50+00:00</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Fix deferred cast checks using the wrong body for determining constness</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2025-10-30T09:33:53+00:00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Show that a test still fails with the feature gate enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2025-10-21T10:17:38+00:00</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Pattern types have their base type as a field</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2024-10-07T12:50:46+00:00</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Bump ui_test</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2024-10-01T13:50:51+00:00</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Avoid a bool and use an Option of ZST instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2024-10-14T14:29:49+00:00</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Avoid some needless monomorphizations</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2024-10-04T18:11:26+00:00</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Prefer refutable slice patterns over len check + index op</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2024-09-16T21:07:18+00:00</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Automatically add/remove labesl when github review (requests) are used</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2024-09-16T08:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Fix run --dep</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2024-09-16T19:10:32+00:00</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Refator DependencyBuilder construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2024-09-07T14:40:08+00:00</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Bump ui test</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2024-09-08T12:43:12+00:00</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Remove an unused piece of logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2024-08-17T19:38:10+00:00</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Bump ui_test</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2024-05-02T10:44:40+00:00</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Bump ui_test to 0.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>oli-obk</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
           <t>2023-08-31T13:42:39+00:00</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>Bump ui_test to 0.20</t>
         </is>
